--- a/Result/profitability/6202.xlsx
+++ b/Result/profitability/6202.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>0.175</v>
+        <v>0.295</v>
       </c>
       <c r="N2" t="n">
-        <v>39.4775</v>
+        <v>40.30125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -693,7 +693,7 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="n">
         <v>97.09999999999999</v>
@@ -780,10 +780,10 @@
         <v>1.01</v>
       </c>
       <c r="M3" t="n">
-        <v>0.34125</v>
+        <v>0.42</v>
       </c>
       <c r="N3" t="n">
-        <v>40.4275</v>
+        <v>41.31875</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.88</v>
       </c>
       <c r="M4" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="N4" t="n">
-        <v>41.33375</v>
+        <v>42.0875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.22</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4275</v>
+        <v>0.495</v>
       </c>
       <c r="N5" t="n">
-        <v>42.5275</v>
+        <v>43.44125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.45875</v>
+        <v>0.5237499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>44.22499999999999</v>
+        <v>45.10125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0.52125</v>
+        <v>0.5824999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>45.7225</v>
+        <v>46.23</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.95</v>
       </c>
       <c r="M8" t="n">
-        <v>0.62125</v>
+        <v>0.66375</v>
       </c>
       <c r="N8" t="n">
-        <v>46.95875</v>
+        <v>47.54625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1772,7 +1772,7 @@
         <v>1.22</v>
       </c>
       <c r="M11" t="n">
-        <v>0.7462500000000001</v>
+        <v>0.74625</v>
       </c>
       <c r="N11" t="n">
         <v>48.535</v>
@@ -1899,10 +1899,10 @@
         <v>0.96</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7562499999999999</v>
+        <v>0.75625</v>
       </c>
       <c r="N12" t="n">
-        <v>48.55625</v>
+        <v>48.55625000000001</v>
       </c>
       <c r="O12" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>0.49</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7899999999999999</v>
+        <v>0.79</v>
       </c>
       <c r="N13" t="n">
         <v>47.87875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6202</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>983</v>
+      </c>
+      <c r="D75" t="n">
+        <v>544</v>
+      </c>
+      <c r="E75" t="n">
+        <v>440</v>
+      </c>
+      <c r="F75" t="n">
+        <v>44.71</v>
+      </c>
+      <c r="G75" t="n">
+        <v>148</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>15.10%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>34</v>
+      </c>
+      <c r="J75" t="n">
+        <v>182</v>
+      </c>
+      <c r="K75" t="n">
+        <v>148</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="N75" t="n">
+        <v>39.35625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.133333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>4.700000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1174706323419146</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>5.399999999999999</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>7.310000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1954545454545455</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
